--- a/data_CMS/CMS_109_TW2_2026.xlsx
+++ b/data_CMS/CMS_109_TW2_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,7 +709,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t xml:space="preserve">Kementerian Imigrasi dan Pemasyarakatan </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -754,27 +754,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>032901004361303</t>
+          <t>032901006291300</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG O</t>
+          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>651544034101000</t>
+          <t>655026927251000</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BPG 109 PA MUARADUA 04</t>
+          <t>BPG 109 RUPBASAN KLS II BATURAJA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -795,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>14196000</v>
+        <v>239957696</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -815,34 +815,32 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>2026</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>TW2</t>
+          <t>TW4</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Master Data</t>
+          <t>MASTER DATA</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>403410</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>403410</t>
-        </is>
-      </c>
+          <t>692725</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -862,17 +860,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BADAN URUSAN ADMINISTRASI</t>
+          <t>Ditjen Badan Peradilan Agama</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -887,27 +885,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>032901004372304</t>
+          <t>032901004361303</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>RKK BUA MA OPS</t>
+          <t>RKK DITJEN BADILAG O</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>653240989631000</t>
+          <t>651544034101000</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BPG 109 PENGADILAN NEGERI BATURAJA</t>
+          <t>BPG 109 PA MUARADUA 04</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -916,10 +914,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>20133224</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -928,14 +926,14 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>533083089</v>
+        <v>14196000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -963,19 +961,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1005,7 +1003,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1020,7 +1018,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1035,12 +1033,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>653244019451000</t>
+          <t>653240989631000</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BPG 109 PA MUARADUA 01</t>
+          <t>BPG 109 PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1049,10 +1047,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>20133224</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,14 +1059,14 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="U5" t="n">
-        <v>394452331</v>
+        <v>533083089</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1096,19 +1094,19 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>923</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1138,7 +1136,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1153,7 +1151,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1168,24 +1166,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>653254019441000</t>
+          <t>653244019451000</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BPG 109 PA MARTAPURA 01</t>
+          <t>BPG 109 PA MUARADUA 01</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10281416</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>306950822</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1194,14 +1192,14 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>394452331</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1229,19 +1227,19 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1271,7 +1269,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1286,7 +1284,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1301,24 +1299,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>653254022671000</t>
+          <t>653254019441000</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BPG 109 Pengadilan Agama Baturaja</t>
+          <t>BPG 109 PA MARTAPURA 01</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>10281416</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>418</v>
+        <v>370</v>
       </c>
       <c r="Q7" t="n">
-        <v>282204390</v>
+        <v>306950822</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1362,19 +1360,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1394,17 +1392,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Umum</t>
+          <t>BADAN URUSAN ADMINISTRASI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1419,39 +1417,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>023001004085304</t>
+          <t>032901004372304</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILUM O</t>
+          <t>RKK BUA MA OPS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>654440992281000</t>
+          <t>653254022671000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BPG 109 PN BATURAJA 03</t>
+          <t>BPG 109 Pengadilan Agama Baturaja</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>282204390</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1460,14 +1458,14 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>258898000</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1495,19 +1493,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1517,27 +1515,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KEJAKSAAN RI</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
+          <t>Ditjen Badan Peradilan Umum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1552,39 +1550,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>019301003441305</t>
+          <t>023001004085304</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>RKK KEJAKSAAN RI OPS</t>
+          <t>RKK DITJEN BADILUM O</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>651320071301000</t>
+          <t>654440992281000</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BPG 109 KEJARI BATURAJA</t>
+          <t>BPG 109 PN BATURAJA 03</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24642429</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1593,14 +1591,14 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="U9" t="n">
-        <v>16762500</v>
+        <v>258898000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1628,19 +1626,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1670,7 +1668,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1685,7 +1683,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1700,24 +1698,24 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>651320071901000</t>
+          <t>651320071301000</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BPG 109 KEJARI OKU TIMUR</t>
+          <t>BPG 109 KEJARI BATURAJA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8868558</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>24642429</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1726,14 +1724,14 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>220455183</v>
+        <v>16762500</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1761,19 +1759,19 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1803,7 +1801,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1818,32 +1816,32 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>019301003871306</t>
+          <t>019301003441305</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>RKP KEJAKSAAN RI</t>
+          <t>RKK KEJAKSAAN RI OPS</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>654030072080000</t>
+          <t>651320071901000</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BPN 109 KN OK ULU SELATAN</t>
+          <t>BPG 109 KEJARI OKU TIMUR</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8868558</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1859,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>220455183</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1871,7 +1869,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1894,19 +1892,19 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1916,27 +1914,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KEMENTERIAN PERTAHANAN</t>
+          <t>KEJAKSAAN RI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MARKAS BESAR TNI AD</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1951,27 +1949,27 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.07.05 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>001801002565308</t>
+          <t>019301003871306</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RKK MABES TNI AD KEM</t>
+          <t>RKP KEJAKSAAN RI</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>652813448941000</t>
+          <t>654030072080000</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BPG 109 RUMKIT TK IV BTA</t>
+          <t>BPN 109 KN OK ULU SELATAN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1980,10 +1978,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3182888700</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1999,12 +1997,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2027,19 +2025,19 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2069,7 +2067,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2084,7 +2082,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>RUMKIT TK. III 02.07.05 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2099,24 +2097,24 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>652816850011000</t>
+          <t>652813448941000</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BPG 109 PUSLATPUR KODIKLATAD</t>
+          <t>BPG 109 RUMKIT TK IV BTA</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>34897500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>4800000</v>
+        <v>3182888700</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2125,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>97063250</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2160,19 +2158,19 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2182,27 +2180,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>KEMENTERIAN PERTAHANAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DITJEN PAJAK</t>
+          <t>MARKAS BESAR TNI AD</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2217,51 +2215,51 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>035901001813300</t>
+          <t>001801002565308</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>RKK DJP KEMENKEU RI</t>
+          <t>RKK MABES TNI AD KEM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>650134105741000</t>
+          <t>652816850011000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KPP BATURAJA </t>
+          <t>BPG 109 PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>18884207</t>
+          <t>34897500</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>354</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>581783149</v>
+        <v>4800000</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>5830480</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>97063250</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2293,19 +2291,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2315,27 +2313,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KESEHATAN</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL KESEHATAN PRIMER DAN KOMUNITAS</t>
+          <t>DITJEN PAJAK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2350,45 +2348,45 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>034101001800302</t>
+          <t>035901001813300</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>RKK DITJEN KESEHATAN MASYARAKAT KEMENKES</t>
+          <t>RKK DJP KEMENKEU RI</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>654146908011000</t>
+          <t>650134105741000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BPG 109 LLKM BATURAJA</t>
+          <t xml:space="preserve">BPG 109 KPP BATURAJA </t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>17722500</t>
+          <t>18884207</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="Q15" t="n">
-        <v>203870310</v>
+        <v>581783149</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>5830480</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2426,19 +2424,19 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2448,34 +2446,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN KESEHATAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DIREKTORAT JENDERAL KESEHATAN PRIMER DAN KOMUNITAS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>440505</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>109</t>
@@ -2483,39 +2481,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>023001004099303</t>
+          <t>034101001800302</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KAT</t>
+          <t>RKK DITJEN KESEHATAN MASYARAKAT KEMENKES</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>651624405051000</t>
+          <t>654146908011000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKUS</t>
+          <t>BPG 109 LLKM BATURAJA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17722500</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="Q16" t="n">
-        <v>11700000</v>
+        <v>203870310</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2559,19 +2557,19 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>690801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2601,7 +2599,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2616,7 +2614,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2631,24 +2629,24 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>651816665041000</t>
+          <t>651624405051000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKUT</t>
+          <t>BPG 109 MENAG06 OKUS</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q17" t="n">
-        <v>7720000</v>
+        <v>11700000</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2657,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1290000</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2692,19 +2690,19 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2724,17 +2722,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT BUDDHA</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2754,34 +2752,34 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>023001004125308</t>
+          <t>023001004099303</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS BUD</t>
+          <t>RKK DITJEN BIMAS KAT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>651886665061000</t>
+          <t>651816665041000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG08 OKUT</t>
+          <t>BPG 109 MENAG06 OKUT</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7720000</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2790,19 +2788,19 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1290000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2825,19 +2823,19 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2857,17 +2855,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT BUDDHA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2882,27 +2880,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>023001004112305</t>
+          <t>023001004125308</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RKK SEKRETARIAT JEND</t>
+          <t>RKK DITJEN BIMAS BUD</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>652594405021000</t>
+          <t>651886665061000</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG01 OKUS</t>
+          <t>BPG 109 MENAG08 OKUT</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2911,10 +2909,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>132407647</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2930,12 +2928,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2958,19 +2956,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3000,7 +2998,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3015,7 +3013,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3030,24 +3028,24 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>652596665011000</t>
+          <t>652594405021000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG01 OKUT</t>
+          <t>BPG 109 MENAG01 OKUS</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4385000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="Q20" t="n">
-        <v>95901340</v>
+        <v>132407647</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3091,19 +3089,19 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3123,17 +3121,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3148,39 +3146,39 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>023001004111309</t>
+          <t>023001004112305</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKA</t>
+          <t>RKK SEKRETARIAT JEND</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>652734184621000</t>
+          <t>652596665011000</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN BANDING AGUNG</t>
+          <t>BPG 109 MENAG01 OKUT</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>4385000</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="Q21" t="n">
-        <v>78277000</v>
+        <v>95901340</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3189,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>92347500</v>
+        <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3224,19 +3222,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3266,7 +3264,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3281,7 +3279,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3296,24 +3294,24 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>652734184711000</t>
+          <t>652734184621000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN CAMPANG TIGA</t>
+          <t>BPG 109 MTSN BANDING AGUNG</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000000</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>78277000</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3322,14 +3320,14 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>130162400</v>
+        <v>92347500</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3357,19 +3355,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3399,7 +3397,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3414,7 +3412,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3429,24 +3427,24 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>652734242451000</t>
+          <t>652734184711000</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BPG 109 MAN BATURAJA</t>
+          <t>BPG 109 MTSN CAMPANG TIGA</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9439948</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>113528777</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3455,14 +3453,14 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>130162400</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3490,19 +3488,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3532,7 +3530,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3547,7 +3545,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3562,24 +3560,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>652734249671000</t>
+          <t>652734242451000</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN MARTAPURA</t>
+          <t>BPG 109 MAN BATURAJA</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9439948</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>113528777</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3588,14 +3586,14 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>259475000</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3623,19 +3621,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3665,7 +3663,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3680,7 +3678,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3695,24 +3693,24 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>652734260501000</t>
+          <t>652734249671000</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN BATURAJA</t>
+          <t>BPG 109 MTSN MARTAPURA</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>147638868</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3721,14 +3719,14 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>259475000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3756,19 +3754,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3798,7 +3796,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3813,7 +3811,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3828,24 +3826,24 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>652734260661000</t>
+          <t>652734260501000</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BPG 109 MAN 1 OKU TIMUR</t>
+          <t>BPG 109 MTSN BATURAJA</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>147638868</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3854,14 +3852,14 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>299099600</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3889,19 +3887,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3931,7 +3929,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3946,7 +3944,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3961,24 +3959,24 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>652734405041000</t>
+          <t>652734260661000</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG OKUS</t>
+          <t>BPG 109 MAN 1 OKU TIMUR</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6900000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>304380000</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3987,14 +3985,14 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>299099600</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4022,19 +4020,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4064,7 +4062,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4079,7 +4077,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4094,24 +4092,24 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>652735530991000</t>
+          <t>652734405041000</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN KOTANEGARA</t>
+          <t>BPG 109 MENAG OKUS</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6900000</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>304380000</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -4120,14 +4118,14 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>116600000</v>
+        <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4155,19 +4153,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4197,7 +4195,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4212,7 +4210,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4227,12 +4225,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>652735743701000</t>
+          <t>652735530991000</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BPG 109 MTsN 3 OKU SELATAN</t>
+          <t>BPG 109 MTSN KOTANEGARA</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -4253,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U29" t="n">
-        <v>113975500</v>
+        <v>116600000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4288,19 +4286,19 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4330,7 +4328,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4345,7 +4343,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4360,12 +4358,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>652735975581000</t>
+          <t>652735743701000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BPG 109 MAN 2 OKU SELATAN</t>
+          <t>BPG 109 MTsN 3 OKU SELATAN</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4374,10 +4372,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>38472385</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4386,14 +4384,14 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>86094900</v>
+        <v>113975500</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4421,19 +4419,19 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4463,7 +4461,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4478,7 +4476,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4493,40 +4491,40 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>652736611921000</t>
+          <t>652735975581000</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN PULAU BERINGIN</t>
+          <t>BPG 109 MAN 2 OKU SELATAN</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>38472385</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>88067500</v>
+        <v>86094900</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4554,19 +4552,19 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4596,7 +4594,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4611,7 +4609,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4626,40 +4624,40 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>652736665031000</t>
+          <t>652736611921000</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG04 OKUT</t>
+          <t>BPG 109 MTSN PULAU BERINGIN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2652000</t>
+          <t>10000000</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>419679960</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>88067500</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4687,19 +4685,19 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4729,7 +4727,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4744,7 +4742,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4759,24 +4757,24 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>652745974801000</t>
+          <t>652736665031000</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN KANGKUNG</t>
+          <t>BPG 109 MENAG04 OKUT</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2652000</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>419679960</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4785,14 +4783,14 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>93616108</v>
+        <v>0</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4820,19 +4818,19 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4852,17 +4850,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4877,39 +4875,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>023001004113301</t>
+          <t>023001004111309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS ISL</t>
+          <t>RKK DITJEN PENDIDIKA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>653004405031000</t>
+          <t>652745974801000</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG OKUS</t>
+          <t>BPG 109 MTSN KANGKUNG</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>17000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>274927870</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4918,14 +4916,14 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>93616108</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4953,19 +4951,19 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4995,7 +4993,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5010,7 +5008,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5025,24 +5023,24 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>653006665021000</t>
+          <t>653004405031000</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG03 OKUT</t>
+          <t>BPG 109 MENAG OKUS</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1480000</t>
+          <t>17000000</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="Q35" t="n">
-        <v>184661897</v>
+        <v>274927870</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -5086,19 +5084,19 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5118,17 +5116,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5143,39 +5141,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>120801000036303</t>
+          <t>023001004113301</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>RKK DITJEN PHU KEMEN</t>
+          <t>RKK DITJEN BIMAS ISL</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>653584405071000</t>
+          <t>653006665021000</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG09 OKUS</t>
+          <t>BPG 109 MENAG03 OKUT</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1480000</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>184661897</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5191,12 +5189,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5219,19 +5217,19 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5261,7 +5259,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5276,7 +5274,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5291,12 +5289,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>653586665071000</t>
+          <t>653584405071000</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG09 OKUT</t>
+          <t>BPG 109 MENAG09 OKUS</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5352,19 +5350,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5384,17 +5382,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
+          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5409,27 +5407,27 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>023001004123306</t>
+          <t>120801000036303</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS HIN</t>
+          <t>RKK DITJEN PHU KEMEN</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>653624405061000</t>
+          <t>653586665071000</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKUS</t>
+          <t>BPG 109 MENAG09 OKUT</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5438,10 +5436,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9600000</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5457,12 +5455,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5485,19 +5483,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5527,7 +5525,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5542,7 +5540,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5557,24 +5555,24 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>653626665051000</t>
+          <t>653624405061000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKUT</t>
+          <t>BPG 109 MENAG07 OKUS</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q39" t="n">
-        <v>8765500</v>
+        <v>9600000</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5618,19 +5616,19 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5650,17 +5648,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KRISTEN</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5680,34 +5678,34 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>036101000868303</t>
+          <t>023001004123306</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KRI</t>
+          <t>RKK DITJEN BIMAS HIN</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>653661110711000</t>
+          <t>653626665051000</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>BPG 109 KEMENAG05</t>
+          <t>BPG 109 MENAG07 OKUT</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2850000</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q40" t="n">
-        <v>5500000</v>
+        <v>8765500</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5751,19 +5749,19 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5773,27 +5771,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KRISTEN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5808,39 +5806,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>026101001822302</t>
+          <t>036101000868303</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>RKK BADAN PUSAT STAT</t>
+          <t>RKK DITJEN BIMAS KRI</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>652074282581000</t>
+          <t>653661110711000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU</t>
+          <t>BPG 109 KEMENAG05</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>29714400</t>
+          <t>2850000</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1175</v>
+        <v>14</v>
       </c>
       <c r="Q41" t="n">
-        <v>704225849</v>
+        <v>5500000</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5849,10 +5847,10 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>12300000</v>
+        <v>0</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -5884,19 +5882,19 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5926,7 +5924,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5941,7 +5939,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5956,24 +5954,24 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>652076672151000</t>
+          <t>652074282581000</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU SELATAN</t>
+          <t>BPG 109 BPS OKU</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1276414</t>
+          <t>29714400</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>139</v>
+        <v>1175</v>
       </c>
       <c r="Q42" t="n">
-        <v>109239120</v>
+        <v>704225849</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5982,10 +5980,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>12300000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6017,19 +6015,19 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6059,7 +6057,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6074,7 +6072,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6089,24 +6087,24 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>652076685291000</t>
+          <t>652076672151000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU TIMUR</t>
+          <t>BPG 109 BPS OKU SELATAN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>123233530</t>
+          <t>1276414</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1490</v>
+        <v>139</v>
       </c>
       <c r="Q43" t="n">
-        <v>898947764</v>
+        <v>109239120</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -6115,10 +6113,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>43236649</v>
+        <v>0</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6150,19 +6148,19 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6172,12 +6170,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>BADAN PUSAT STATISTIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6187,12 +6185,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>BADAN PUSAT STATISTIK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6207,39 +6205,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>019301003440309</t>
+          <t>026101001822302</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>RKK SETJEN ATR OPS</t>
+          <t>RKK BADAN PUSAT STAT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>650666690551000</t>
+          <t>652076685291000</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR PERTANAHAN OKUT</t>
+          <t>BPG 109 BPS OKU TIMUR</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>17916969</t>
+          <t>123233530</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>65</v>
+        <v>1490</v>
       </c>
       <c r="Q44" t="n">
-        <v>32549075</v>
+        <v>898947764</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -6248,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
-        <v>242789416</v>
+        <v>43236649</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6283,19 +6281,19 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6305,12 +6303,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6320,12 +6318,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6340,39 +6338,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>019301003548301</t>
+          <t>019301003440309</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>RKK POLRI OPS</t>
+          <t>RKK SETJEN ATR OPS</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>652376416811000</t>
+          <t>650666690551000</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKU</t>
+          <t>BPG 109 KANTOR PERTANAHAN OKUT</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17916969</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>32549075</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6381,19 +6379,19 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>242789416</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -6416,19 +6414,19 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6458,7 +6456,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6473,7 +6471,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6488,24 +6486,24 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>652376652921000</t>
+          <t>652376416811000</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKUT</t>
+          <t>BPG 109 POLRES OKU</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>185527704</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>55678598</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6514,19 +6512,19 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>5024716106</v>
+        <v>0</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -6549,19 +6547,19 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6591,7 +6589,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6606,7 +6604,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6621,24 +6619,24 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>652376653071000</t>
+          <t>652376652921000</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKU SELATAN</t>
+          <t>BPG 109 POLRES OKUT</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>220000000</t>
+          <t>185527704</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="Q47" t="n">
-        <v>310210000</v>
+        <v>55678598</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6647,10 +6645,10 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="U47" t="n">
-        <v>4332775639</v>
+        <v>5024716106</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -6682,19 +6680,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6704,12 +6702,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL</t>
+          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6719,12 +6717,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL</t>
+          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6739,39 +6737,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>034001002800301</t>
+          <t>019301003548301</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>RKK BNN OPS</t>
+          <t>RKK POLRI OPS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>650901110791000</t>
+          <t>652376653071000</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>BPG 109 BNNK OKUT MARTAPURA</t>
+          <t>BPG 109 POLRES OKU SELATAN</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10385944</t>
+          <t>220000000</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="Q48" t="n">
-        <v>235865601</v>
+        <v>310210000</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6780,10 +6778,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4332775639</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -6815,19 +6813,19 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6837,12 +6835,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN NARKOTIKA NASIONAL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6852,12 +6850,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN NARKOTIKA NASIONAL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6872,45 +6870,45 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>050601000144309</t>
+          <t>034001002800301</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMU</t>
+          <t>RKK BNN OPS</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>651896565531000</t>
+          <t>650901110791000</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKU</t>
+          <t>BPG 109 BNNK OKUT MARTAPURA</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>10385944</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="Q49" t="n">
-        <v>69465184</v>
+        <v>235865601</v>
       </c>
       <c r="R49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1992710</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -6948,19 +6946,19 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6990,7 +6988,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7005,7 +7003,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7020,30 +7018,30 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>651896565601000</t>
+          <t>651896565531000</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKUT</t>
+          <t>BPG 109 KPU OKU</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="Q50" t="n">
-        <v>95842429</v>
+        <v>69465184</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1992710</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -7081,19 +7079,19 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7103,27 +7101,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN </t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7138,39 +7136,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>032901006291300</t>
+          <t>050601000144309</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
+          <t>KOMISI PEMILIHAN UMU</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>655026923341000</t>
+          <t>651896565601000</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>BPG 109 LP KLS IIB MUARADUA</t>
+          <t>BPG 109 KPU OKUT</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>95842429</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -7179,14 +7177,14 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>324000000</v>
+        <v>0</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7214,19 +7212,19 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7256,7 +7254,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7271,7 +7269,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7286,24 +7284,24 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>655026923391000</t>
+          <t>655026923341000</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>BPG 109 RUTAN KLS IIB BATURAJA</t>
+          <t>BPG 109 LP KLS IIB MUARADUA</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2199620</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>98966152</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -7312,14 +7310,14 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>324000000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7347,19 +7345,19 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7389,7 +7387,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7404,7 +7402,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7419,24 +7417,24 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>655026923401000</t>
+          <t>655026923391000</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>BPG 109 LP KLS IIB MARTAPURA</t>
+          <t>BPG 109 RUTAN KLS IIB BATURAJA</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2992280</t>
+          <t>2199620</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="Q53" t="n">
-        <v>8235954</v>
+        <v>98966152</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7445,10 +7443,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>182353120</v>
+        <v>0</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7480,19 +7478,19 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7522,7 +7520,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7537,7 +7535,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7552,24 +7550,24 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>655026926251000</t>
+          <t>655026923401000</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>BPG 109 BAPAS KLS II OKU INDUK</t>
+          <t>BPG 109 LP KLS IIB MARTAPURA</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2992280</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="Q54" t="n">
-        <v>25092500</v>
+        <v>8235954</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7578,10 +7576,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U54" t="n">
-        <v>33250000</v>
+        <v>182353120</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7613,49 +7611,49 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BNI</t>
+          <t>BRI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BADAN PENGAWASAN PEMILIHAN UMUM</t>
+          <t xml:space="preserve">KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sekretariat Jenderal Badan Pengawas Pemilihan Umum</t>
+          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7670,39 +7668,39 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>969549335</t>
+          <t>032901006291300</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RKK BAWASLU OPS                  PEMERINTAH</t>
+          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>9890714190061000</t>
+          <t>655026926251000</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>BPG 109 SEKRET. BAWASLU KAB OKU</t>
+          <t>BPG 109 BAPAS KLS II OKU INDUK</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>1150000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="Q55" t="n">
-        <v>59877555</v>
+        <v>25092500</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -7711,10 +7709,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>4322500</v>
+        <v>33250000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -7746,19 +7744,19 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7788,7 +7786,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7803,39 +7801,39 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2222227732</t>
+          <t>969549335</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>RKL SETJEN BAWASLU PDHL</t>
+          <t>RKK BAWASLU OPS                  PEMERINTAH</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>9897326865032401</t>
+          <t>9890714190061000</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>RPL109 PDHL PILBUP OKUS 2QPDXATA</t>
+          <t>BPG 109 SEKRET. BAWASLU KAB OKU</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1150000</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>59877555</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -7844,19 +7842,19 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>4322500</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -7879,19 +7877,19 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7901,12 +7899,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN PENGAWASAN PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7916,12 +7914,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>Sekretariat Jenderal Badan Pengawas Pemilihan Umum</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7936,39 +7934,39 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>976288077</t>
+          <t>2222227732</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>RKK KOMISI PEMILIHAN UMUM OPS           LAIN-LAIN</t>
+          <t>RKL SETJEN BAWASLU PDHL</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>9890766565741000</t>
+          <t>9897326865032401</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKUS</t>
+          <t>RPL109 PDHL PILBUP OKUS 2QPDXATA</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>1785000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>60329827</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -7977,19 +7975,19 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>52206500</v>
+        <v>0</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -8012,19 +8010,19 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8034,12 +8032,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8049,12 +8047,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8069,39 +8067,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2020090032</t>
+          <t>976288077</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>RKK KOMISI PEMILIHAN UMUM OPS           LAIN-LAIN</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>9890356705611000</t>
+          <t>9890766565741000</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KANTAH OKUS </t>
+          <t>BPG 109 KPU OKUS</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>6936601</t>
+          <t>1785000</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="Q58" t="n">
-        <v>144135223</v>
+        <v>60329827</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -8110,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="U58" t="n">
-        <v>48074833</v>
+        <v>52206500</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8145,19 +8143,19 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8167,27 +8165,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8202,39 +8200,39 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>6072020860</t>
+          <t>2020090032</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS      PEMERINTAH</t>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>9891225537921000</t>
+          <t>9890356705611000</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN 1 OKU SELATAN</t>
+          <t xml:space="preserve">BPG 109 KANTAH OKUS </t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>13573000</t>
+          <t>6936601</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="Q59" t="n">
-        <v>58000</v>
+        <v>144135223</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8243,10 +8241,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>429241000</v>
+        <v>48074833</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8278,19 +8276,19 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8320,7 +8318,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8335,7 +8333,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -8350,24 +8348,24 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>9891226621271000</t>
+          <t>9891225537921000</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 MANMUARADUA </t>
+          <t>BPG 109 MTSN 1 OKU SELATAN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13573000</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -8376,14 +8374,14 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="U60" t="n">
-        <v>81278880</v>
+        <v>429241000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8411,49 +8409,49 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bank Mandiri</t>
+          <t>BNI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KEMENTERIAN TRANSMIGRASI</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL PEMBANGUNAN DAN PENGEMBANGAN KAWASAN TRANSMIGRASI</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8468,27 +8466,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Dinas Tenaga Kerja dan Transmgirasi Kabupaten Ogan Komering Ulu Timur</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1240018189994</t>
+          <t>6072020860</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>RKK DITJEN PPKTRANS</t>
+          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS      PEMERINTAH</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>8100126916531000</t>
+          <t>9891226621271000</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>BPG 109 DINAKERTRANS KAB OKU TIMUR</t>
+          <t xml:space="preserve">BPG 109 MANMUARADUA </t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8509,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>81278880</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8521,7 +8519,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -8544,19 +8542,19 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8566,12 +8564,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN TRANSMIGRASI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8581,12 +8579,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
+          <t>DIREKTORAT JENDERAL PEMBANGUNAN DAN PENGEMBANGAN KAWASAN TRANSMIGRASI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8601,39 +8599,39 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>Dinas Tenaga Kerja dan Transmgirasi Kabupaten Ogan Komering Ulu Timur</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1030093939342</t>
+          <t>1240018189994</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS ISLAM KEMENAG OPS</t>
+          <t>RKK DITJEN PPKTRANS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>8100124184571000</t>
+          <t>8100126916531000</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG03 OKU</t>
+          <t>BPG 109 DINAKERTRANS KAB OKU TIMUR</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>7500000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>178181713</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -8649,12 +8647,12 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -8677,19 +8675,19 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8709,17 +8707,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8739,34 +8737,34 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1030093939367</t>
+          <t>1030093939342</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS ISLAM KEMENAG OPS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>8100124184601000</t>
+          <t>8100124184571000</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKU</t>
+          <t>BPG 109 MENAG03 OKU</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7500000</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>178181713</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8782,12 +8780,12 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -8810,19 +8808,19 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8842,17 +8840,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8872,22 +8870,22 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1030009004009</t>
+          <t>1030093939367</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>RKK DITJEN PHU KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>8100124184611000</t>
+          <t>8100124184601000</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG 09 OKU</t>
+          <t>BPG 109 MENAG07 OKU</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -8943,19 +8941,19 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8975,17 +8973,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9000,39 +8998,39 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KOTA PALEMBANG</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1030093939391</t>
+          <t>1030009004009</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS</t>
+          <t>RKK DITJEN PHU KEMENAG OPS</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>8100124184581000</t>
+          <t>8100124184611000</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>BPG109 MENAG 04 OKU</t>
+          <t>BPG 109 MENAG 09 OKU</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>3655100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>160287701</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -9048,12 +9046,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -9076,19 +9074,19 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9098,12 +9096,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -9113,12 +9111,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9133,39 +9131,39 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KOTA PALEMBANG</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1190066371202</t>
+          <t>1030093939391</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG OPS</t>
+          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>8100124022681000</t>
+          <t>8100124184581000</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>BPG 109 PA_BATURAJA_BPU</t>
+          <t>BPG109 MENAG 04 OKU</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3655100</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="Q66" t="n">
-        <v>23880000</v>
+        <v>160287701</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -9209,19 +9207,19 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9231,34 +9229,34 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ditjen Badan Peradilan Agama</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>402268</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>418459</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>109</t>
@@ -9266,27 +9264,27 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1030055695569</t>
+          <t>1190066371202</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KATOLIK KEMENAG OPS</t>
+          <t>RKK DITJEN BADILAG OPS</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>8100124184591000</t>
+          <t>8100124022681000</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKU</t>
+          <t>BPG 109 PA_BATURAJA_BPU</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -9295,10 +9293,10 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="Q67" t="n">
-        <v>20564000</v>
+        <v>23880000</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -9342,19 +9340,19 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>402268</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9374,17 +9372,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9404,34 +9402,34 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1030093939334</t>
+          <t>1030055695569</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>RKK SEKRETARIAT JENDERAL KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS KATOLIK KEMENAG OPS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>8100124184561000</t>
+          <t>8100124184591000</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG 01 OKU</t>
+          <t>BPG 109 MENAG06 OKU</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>4825000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="Q68" t="n">
-        <v>153367917</v>
+        <v>20564000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -9475,19 +9473,19 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9497,12 +9495,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -9517,7 +9515,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9532,39 +9530,39 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1260007919292</t>
+          <t>1030093939334</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>RKK SETJEN ATR OPS</t>
+          <t>RKK SEKRETARIAT JENDERAL KEMENAG OPS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>8100124311421000</t>
+          <t>8100124184561000</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KANTAH OKU </t>
+          <t>BPG 109 MENAG 01 OKU</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>4825000</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="Q69" t="n">
-        <v>26856800</v>
+        <v>153367917</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -9573,10 +9571,10 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>381093872</v>
+        <v>0</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -9608,19 +9606,19 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9630,27 +9628,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DITJEN PERBENDAHARAAN</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9665,39 +9663,39 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1030020030009</t>
+          <t>1260007919292</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>RKK DITJEN PERBENDAHARAAN</t>
+          <t>RKK SETJEN ATR OPS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>8100125279751000</t>
+          <t>8100124311421000</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>BPG 109 KPPN BATURAJA</t>
+          <t xml:space="preserve">BPG 109 KANTAH OKU </t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>16141635</t>
+          <t>450</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="Q70" t="n">
-        <v>115384194</v>
+        <v>26856800</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -9706,10 +9704,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U70" t="n">
-        <v>177094803</v>
+        <v>381093872</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -9741,49 +9739,49 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BSI</t>
+          <t>Bank Mandiri</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>DITJEN PERBENDAHARAAN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9798,39 +9796,39 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1999299918</t>
+          <t>1030020030009</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>RKK KEMENHAJ RI OPS</t>
+          <t>RKK DITJEN PERBENDAHARAAN</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>8101626951821000</t>
+          <t>8100125279751000</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU TIMUR</t>
+          <t>BPG 109 KPPN BATURAJA</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>5948000</t>
+          <t>16141635</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q71" t="n">
-        <v>215651538</v>
+        <v>115384194</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -9839,10 +9837,10 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>177094803</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -9856,7 +9854,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="Y71" t="n">
@@ -9874,19 +9872,19 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9916,7 +9914,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9931,7 +9929,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9946,24 +9944,24 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>8101626951761000</t>
+          <t>8101626951821000</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU</t>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>5896000</t>
+          <t>5948000</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="Q72" t="n">
-        <v>361790608</v>
+        <v>215651538</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -10007,19 +10005,19 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10029,27 +10027,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t>KEMENTERIAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10064,39 +10062,39 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>7811122275</t>
+          <t>1999299918</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG OPS</t>
+          <t>RKK KEMENHAJ RI OPS</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>8100124034091000</t>
+          <t>8101626951761000</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>BPG 109 PA MARTAPURA 04</t>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>1602000</t>
+          <t>5896000</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="Q73" t="n">
-        <v>49172000</v>
+        <v>361790608</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -10140,19 +10138,19 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10162,27 +10160,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>Ditjen Badan Peradilan Agama</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10197,39 +10195,39 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1999299918</t>
+          <t>7811122275</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>RKK KEMENHAJ RI OPS</t>
+          <t>RKK DITJEN BADILAG OPS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>8101626951841000</t>
+          <t>8100124034091000</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU SELATAN</t>
+          <t>BPG 109 PA MARTAPURA 04</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>6000000</t>
+          <t>1602000</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="Q74" t="n">
-        <v>99752552</v>
+        <v>49172000</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -10273,10 +10271,143 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
+          <t>403409</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>403409</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>27057</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BSI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>695184</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1999299918</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>RKK KEMENHAJ RI OPS</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>8101626951841000</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>6000000</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>99752552</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Aktif CMS</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Aktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>TW2</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>695184</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
         <is>
           <t>695184</t>
         </is>

--- a/data_CMS/CMS_109_TW2_2026.xlsx
+++ b/data_CMS/CMS_109_TW2_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,7 +840,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t xml:space="preserve">Kementerian Imigrasi dan Pemasyarakatan </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -885,27 +885,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>032901004361303</t>
+          <t>032901006291300</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG O</t>
+          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>651544034101000</t>
+          <t>655026927251000</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BPG 109 PA MUARADUA 04</t>
+          <t>BPG 109 RUPBASAN KLS II BATURAJA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>14196000</v>
+        <v>239957696</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -946,34 +946,32 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>2026</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>TW2</t>
+          <t>TW4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Master Data</t>
+          <t>MASTER DATA</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>403410</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>403410</t>
-        </is>
-      </c>
+          <t>692725</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -993,17 +991,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BADAN URUSAN ADMINISTRASI</t>
+          <t>Ditjen Badan Peradilan Agama</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1018,27 +1016,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>032901004372304</t>
+          <t>032901004361303</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>RKK BUA MA OPS</t>
+          <t>RKK DITJEN BADILAG O</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>653240989631000</t>
+          <t>651544034101000</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BPG 109 PENGADILAN NEGERI BATURAJA</t>
+          <t>BPG 109 PA MUARADUA 04</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1047,10 +1045,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20133224</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1059,14 +1057,14 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>533083089</v>
+        <v>14196000</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1094,19 +1092,19 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>403410</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1136,7 +1134,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1151,7 +1149,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1166,12 +1164,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>653244019451000</t>
+          <t>653240989631000</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BPG 109 PA MUARADUA 01</t>
+          <t>BPG 109 PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1180,10 +1178,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>20133224</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1192,14 +1190,14 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="U6" t="n">
-        <v>394452331</v>
+        <v>533083089</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1227,19 +1225,19 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>098963</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>923</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1269,7 +1267,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1284,7 +1282,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1299,24 +1297,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>653254019441000</t>
+          <t>653244019451000</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BPG 109 PA MARTAPURA 01</t>
+          <t>BPG 109 PA MUARADUA 01</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10281416</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>306950822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1325,14 +1323,14 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>394452331</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1360,19 +1358,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>401945</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,7 +1415,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1432,24 +1430,24 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>653254022671000</t>
+          <t>653254019441000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BPG 109 Pengadilan Agama Baturaja</t>
+          <t>BPG 109 PA MARTAPURA 01</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>10281416</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>418</v>
+        <v>370</v>
       </c>
       <c r="Q8" t="n">
-        <v>282204390</v>
+        <v>306950822</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1493,19 +1491,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,17 +1523,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Umum</t>
+          <t>BADAN URUSAN ADMINISTRASI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1550,39 +1548,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>023001004085304</t>
+          <t>032901004372304</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILUM O</t>
+          <t>RKK BUA MA OPS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>654440992281000</t>
+          <t>653254022671000</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BPG 109 PN BATURAJA 03</t>
+          <t>BPG 109 Pengadilan Agama Baturaja</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>282204390</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1591,14 +1589,14 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>258898000</v>
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1626,19 +1624,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1648,27 +1646,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KEJAKSAAN RI</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
+          <t>Ditjen Badan Peradilan Umum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1683,39 +1681,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>019301003441305</t>
+          <t>023001004085304</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>RKK KEJAKSAAN RI OPS</t>
+          <t>RKK DITJEN BADILUM O</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>651320071301000</t>
+          <t>654440992281000</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BPG 109 KEJARI BATURAJA</t>
+          <t>BPG 109 PN BATURAJA 03</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24642429</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1724,14 +1722,14 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="U10" t="n">
-        <v>16762500</v>
+        <v>258898000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1759,19 +1757,19 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>099228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1801,7 +1799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1816,7 +1814,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1831,24 +1829,24 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>651320071901000</t>
+          <t>651320071301000</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BPG 109 KEJARI OKU TIMUR</t>
+          <t>BPG 109 KEJARI BATURAJA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>8868558</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>24642429</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1857,14 +1855,14 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>220455183</v>
+        <v>16762500</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1892,19 +1890,19 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>007130</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1934,7 +1932,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1949,32 +1947,32 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>019301003871306</t>
+          <t>019301003441305</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RKP KEJAKSAAN RI</t>
+          <t>RKK KEJAKSAAN RI OPS</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>654030072080000</t>
+          <t>651320071901000</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BPN 109 KN OK ULU SELATAN</t>
+          <t>BPG 109 KEJARI OKU TIMUR</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8868558</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1990,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>220455183</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2002,7 +2000,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2025,19 +2023,19 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007190</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2047,27 +2045,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KEMENTERIAN PERTAHANAN</t>
+          <t>KEJAKSAAN RI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARKAS BESAR TNI AD</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2082,27 +2080,27 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.07.05 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>001801002565308</t>
+          <t>019301003871306</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>RKK MABES TNI AD KEM</t>
+          <t>RKP KEJAKSAAN RI</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>652813448941000</t>
+          <t>654030072080000</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BPG 109 RUMKIT TK IV BTA</t>
+          <t>BPN 109 KN OK ULU SELATAN</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2111,10 +2109,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3182888700</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2130,12 +2128,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2158,19 +2156,19 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>007208</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2200,7 +2198,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2215,7 +2213,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>RUMKIT TK. III 02.07.05 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2230,24 +2228,24 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>652816850011000</t>
+          <t>652813448941000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BPG 109 PUSLATPUR KODIKLATAD</t>
+          <t>BPG 109 RUMKIT TK IV BTA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>34897500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>4800000</v>
+        <v>3182888700</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2256,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>97063250</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2291,19 +2289,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>344894</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2313,27 +2311,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>KEMENTERIAN PERTAHANAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DITJEN PAJAK</t>
+          <t>MARKAS BESAR TNI AD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2348,51 +2346,51 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>035901001813300</t>
+          <t>001801002565308</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>RKK DJP KEMENKEU RI</t>
+          <t>RKK MABES TNI AD KEM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>650134105741000</t>
+          <t>652816850011000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KPP BATURAJA </t>
+          <t>BPG 109 PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>18884207</t>
+          <t>34897500</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>354</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>581783149</v>
+        <v>4800000</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>5830480</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>97063250</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2424,19 +2422,19 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2446,27 +2444,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KESEHATAN</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL KESEHATAN PRIMER DAN KOMUNITAS</t>
+          <t>DITJEN PAJAK</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2481,45 +2479,45 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>034101001800302</t>
+          <t>035901001813300</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>RKK DITJEN KESEHATAN MASYARAKAT KEMENKES</t>
+          <t>RKK DJP KEMENKEU RI</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>654146908011000</t>
+          <t>650134105741000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BPG 109 LLKM BATURAJA</t>
+          <t xml:space="preserve">BPG 109 KPP BATURAJA </t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17722500</t>
+          <t>18884207</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="Q16" t="n">
-        <v>203870310</v>
+        <v>581783149</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5830480</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2557,19 +2555,19 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2579,34 +2577,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN KESEHATAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DIREKTORAT JENDERAL KESEHATAN PRIMER DAN KOMUNITAS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>440505</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>109</t>
@@ -2614,39 +2612,39 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>023001004099303</t>
+          <t>034101001800302</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KAT</t>
+          <t>RKK DITJEN KESEHATAN MASYARAKAT KEMENKES</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>651624405051000</t>
+          <t>654146908011000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKUS</t>
+          <t>BPG 109 LLKM BATURAJA</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17722500</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="Q17" t="n">
-        <v>11700000</v>
+        <v>203870310</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2690,19 +2688,19 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>690801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2732,7 +2730,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2747,7 +2745,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2762,24 +2760,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>651816665041000</t>
+          <t>651624405051000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKUT</t>
+          <t>BPG 109 MENAG06 OKUS</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
-        <v>7720000</v>
+        <v>11700000</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2788,10 +2786,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1290000</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2823,19 +2821,19 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440505</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2855,17 +2853,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT BUDDHA</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2885,34 +2883,34 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>023001004125308</t>
+          <t>023001004099303</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS BUD</t>
+          <t>RKK DITJEN BIMAS KAT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>651886665061000</t>
+          <t>651816665041000</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG08 OKUT</t>
+          <t>BPG 109 MENAG06 OKUT</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7720000</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2921,19 +2919,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1290000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2956,19 +2954,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>666506</t>
+          <t>666504</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2988,17 +2986,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT BUDDHA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3013,27 +3011,27 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>023001004112305</t>
+          <t>023001004125308</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>RKK SEKRETARIAT JEND</t>
+          <t>RKK DITJEN BIMAS BUD</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>652594405021000</t>
+          <t>651886665061000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG01 OKUS</t>
+          <t>BPG 109 MENAG08 OKUT</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3042,10 +3040,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>132407647</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3061,12 +3059,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3089,19 +3087,19 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666506</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3131,7 +3129,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3146,7 +3144,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3161,24 +3159,24 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>652596665011000</t>
+          <t>652594405021000</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG01 OKUT</t>
+          <t>BPG 109 MENAG01 OKUS</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4385000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="Q21" t="n">
-        <v>95901340</v>
+        <v>132407647</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3222,19 +3220,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>440502</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3254,17 +3252,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3279,39 +3277,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>023001004111309</t>
+          <t>023001004112305</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKA</t>
+          <t>RKK SEKRETARIAT JEND</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>652734184621000</t>
+          <t>652596665011000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN BANDING AGUNG</t>
+          <t>BPG 109 MENAG01 OKUT</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>4385000</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="Q22" t="n">
-        <v>78277000</v>
+        <v>95901340</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3320,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>92347500</v>
+        <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3355,19 +3353,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666501</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3397,7 +3395,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3412,7 +3410,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3427,24 +3425,24 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>652734184711000</t>
+          <t>652734184621000</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN CAMPANG TIGA</t>
+          <t>BPG 109 MTSN BANDING AGUNG</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000000</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>78277000</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3453,14 +3451,14 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>130162400</v>
+        <v>92347500</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3488,19 +3486,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418462</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3530,7 +3528,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3545,7 +3543,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3560,24 +3558,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>652734242451000</t>
+          <t>652734184711000</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BPG 109 MAN BATURAJA</t>
+          <t>BPG 109 MTSN CAMPANG TIGA</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>9439948</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>113528777</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3586,14 +3584,14 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>130162400</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3621,19 +3619,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>418471</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3663,7 +3661,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3678,7 +3676,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3693,24 +3691,24 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>652734249671000</t>
+          <t>652734242451000</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN MARTAPURA</t>
+          <t>BPG 109 MAN BATURAJA</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9439948</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>113528777</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3719,14 +3717,14 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>259475000</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3754,19 +3752,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>424245</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3796,7 +3794,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3811,7 +3809,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3826,24 +3824,24 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>652734260501000</t>
+          <t>652734249671000</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN BATURAJA</t>
+          <t>BPG 109 MTSN MARTAPURA</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>147638868</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3852,14 +3850,14 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>259475000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3887,19 +3885,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3929,7 +3927,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3944,7 +3942,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3959,24 +3957,24 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>652734260661000</t>
+          <t>652734260501000</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BPG 109 MAN 1 OKU TIMUR</t>
+          <t>BPG 109 MTSN BATURAJA</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>147638868</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3985,14 +3983,14 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>299099600</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4020,19 +4018,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>426050</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4062,7 +4060,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4077,7 +4075,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4092,24 +4090,24 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>652734405041000</t>
+          <t>652734260661000</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG OKUS</t>
+          <t>BPG 109 MAN 1 OKU TIMUR</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>6900000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>304380000</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -4118,14 +4116,14 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>299099600</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4153,19 +4151,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>426066</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4195,7 +4193,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4210,7 +4208,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4225,24 +4223,24 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>652735530991000</t>
+          <t>652734405041000</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN KOTANEGARA</t>
+          <t>BPG 109 MENAG OKUS</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6900000</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>304380000</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4251,14 +4249,14 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>116600000</v>
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4286,19 +4284,19 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>440504</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4328,7 +4326,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4343,7 +4341,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4358,12 +4356,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>652735743701000</t>
+          <t>652735530991000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BPG 109 MTsN 3 OKU SELATAN</t>
+          <t>BPG 109 MTSN KOTANEGARA</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4384,10 +4382,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>113975500</v>
+        <v>116600000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4419,19 +4417,19 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4461,7 +4459,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4476,7 +4474,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4491,12 +4489,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>652735975581000</t>
+          <t>652735743701000</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>BPG 109 MAN 2 OKU SELATAN</t>
+          <t>BPG 109 MTsN 3 OKU SELATAN</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4505,10 +4503,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>38472385</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4517,14 +4515,14 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
-        <v>86094900</v>
+        <v>113975500</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4552,19 +4550,19 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4594,7 +4592,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4609,7 +4607,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4624,40 +4622,40 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>652736611921000</t>
+          <t>652735975581000</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN PULAU BERINGIN</t>
+          <t>BPG 109 MAN 2 OKU SELATAN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>10000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>38472385</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>88067500</v>
+        <v>86094900</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4685,19 +4683,19 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>597558</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4727,7 +4725,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4742,7 +4740,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4757,40 +4755,40 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>652736665031000</t>
+          <t>652736611921000</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG04 OKUT</t>
+          <t>BPG 109 MTSN PULAU BERINGIN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2652000</t>
+          <t>10000000</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>419679960</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>88067500</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4818,19 +4816,19 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>661192</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4860,7 +4858,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4875,7 +4873,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4890,24 +4888,24 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>652745974801000</t>
+          <t>652736665031000</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN KANGKUNG</t>
+          <t>BPG 109 MENAG04 OKUT</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2652000</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>419679960</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4916,14 +4914,14 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>93616108</v>
+        <v>0</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4951,19 +4949,19 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4983,17 +4981,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5008,39 +5006,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>023001004113301</t>
+          <t>023001004111309</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS ISL</t>
+          <t>RKK DITJEN PENDIDIKA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>653004405031000</t>
+          <t>652745974801000</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG OKUS</t>
+          <t>BPG 109 MTSN KANGKUNG</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>17000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>274927870</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -5049,14 +5047,14 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>93616108</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5084,19 +5082,19 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>597480</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5126,7 +5124,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5141,7 +5139,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5156,24 +5154,24 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>653006665021000</t>
+          <t>653004405031000</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG03 OKUT</t>
+          <t>BPG 109 MENAG OKUS</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1480000</t>
+          <t>17000000</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="Q36" t="n">
-        <v>184661897</v>
+        <v>274927870</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5217,19 +5215,19 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440503</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5249,17 +5247,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5274,39 +5272,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>120801000036303</t>
+          <t>023001004113301</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>RKK DITJEN PHU KEMEN</t>
+          <t>RKK DITJEN BIMAS ISL</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>653584405071000</t>
+          <t>653006665021000</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG09 OKUS</t>
+          <t>BPG 109 MENAG03 OKUT</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1480000</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>184661897</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5322,12 +5320,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -5350,19 +5348,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666502</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5392,7 +5390,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5407,7 +5405,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5422,12 +5420,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>653586665071000</t>
+          <t>653584405071000</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG09 OKUT</t>
+          <t>BPG 109 MENAG09 OKUS</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5483,19 +5481,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440507</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5515,17 +5513,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
+          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5540,27 +5538,27 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>023001004123306</t>
+          <t>120801000036303</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS HIN</t>
+          <t>RKK DITJEN PHU KEMEN</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>653624405061000</t>
+          <t>653586665071000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKUS</t>
+          <t>BPG 109 MENAG09 OKUT</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5569,10 +5567,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>9600000</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5588,12 +5586,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5616,19 +5614,19 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666507</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5658,7 +5656,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5673,7 +5671,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5688,24 +5686,24 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>653626665051000</t>
+          <t>653624405061000</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKUT</t>
+          <t>BPG 109 MENAG07 OKUS</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q40" t="n">
-        <v>8765500</v>
+        <v>9600000</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5749,19 +5747,19 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5781,17 +5779,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KRISTEN</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5811,34 +5809,34 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>036101000868303</t>
+          <t>023001004123306</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KRI</t>
+          <t>RKK DITJEN BIMAS HIN</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>653661110711000</t>
+          <t>653626665051000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>BPG 109 KEMENAG05</t>
+          <t>BPG 109 MENAG07 OKUT</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2850000</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>5500000</v>
+        <v>8765500</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5882,19 +5880,19 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>666505</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5904,27 +5902,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KRISTEN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5939,39 +5937,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>026101001822302</t>
+          <t>036101000868303</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>RKK BADAN PUSAT STAT</t>
+          <t>RKK DITJEN BIMAS KRI</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>652074282581000</t>
+          <t>653661110711000</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU</t>
+          <t>BPG 109 KEMENAG05</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>29714400</t>
+          <t>2850000</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1175</v>
+        <v>14</v>
       </c>
       <c r="Q42" t="n">
-        <v>704225849</v>
+        <v>5500000</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5980,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>12300000</v>
+        <v>0</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6015,19 +6013,19 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6057,7 +6055,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6072,7 +6070,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6087,24 +6085,24 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>652076672151000</t>
+          <t>652074282581000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU SELATAN</t>
+          <t>BPG 109 BPS OKU</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1276414</t>
+          <t>29714400</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>139</v>
+        <v>1175</v>
       </c>
       <c r="Q43" t="n">
-        <v>109239120</v>
+        <v>704225849</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -6113,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>12300000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6148,19 +6146,19 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6190,7 +6188,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6205,7 +6203,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6220,24 +6218,24 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>652076685291000</t>
+          <t>652076672151000</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>BPG 109 BPS OKU TIMUR</t>
+          <t>BPG 109 BPS OKU SELATAN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>123233530</t>
+          <t>1276414</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1490</v>
+        <v>139</v>
       </c>
       <c r="Q44" t="n">
-        <v>898947764</v>
+        <v>109239120</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -6246,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>43236649</v>
+        <v>0</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6281,19 +6279,19 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>667215</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6303,12 +6301,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>BADAN PUSAT STATISTIK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6318,12 +6316,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>BADAN PUSAT STATISTIK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6338,39 +6336,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>019301003440309</t>
+          <t>026101001822302</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>RKK SETJEN ATR OPS</t>
+          <t>RKK BADAN PUSAT STAT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>650666690551000</t>
+          <t>652076685291000</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR PERTANAHAN OKUT</t>
+          <t>BPG 109 BPS OKU TIMUR</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>17916969</t>
+          <t>123233530</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>65</v>
+        <v>1490</v>
       </c>
       <c r="Q45" t="n">
-        <v>32549075</v>
+        <v>898947764</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6379,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="U45" t="n">
-        <v>242789416</v>
+        <v>43236649</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6414,19 +6412,19 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6436,12 +6434,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6451,12 +6449,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6471,39 +6469,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>019301003548301</t>
+          <t>019301003440309</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>RKK POLRI OPS</t>
+          <t>RKK SETJEN ATR OPS</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>652376416811000</t>
+          <t>650666690551000</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKU</t>
+          <t>BPG 109 KANTOR PERTANAHAN OKUT</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17916969</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>32549075</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6512,19 +6510,19 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>242789416</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -6547,19 +6545,19 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>669055</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6589,7 +6587,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6604,7 +6602,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6619,24 +6617,24 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>652376652921000</t>
+          <t>652376416811000</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKUT</t>
+          <t>BPG 109 POLRES OKU</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>185527704</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>55678598</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6645,19 +6643,19 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>5024716106</v>
+        <v>0</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -6680,19 +6678,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6722,7 +6720,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6737,7 +6735,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6752,24 +6750,24 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>652376653071000</t>
+          <t>652376652921000</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>BPG 109 POLRES OKU SELATAN</t>
+          <t>BPG 109 POLRES OKUT</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>220000000</t>
+          <t>185527704</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="Q48" t="n">
-        <v>310210000</v>
+        <v>55678598</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6778,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="U48" t="n">
-        <v>4332775639</v>
+        <v>5024716106</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -6813,19 +6811,19 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>665292</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6835,12 +6833,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL</t>
+          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6850,12 +6848,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL</t>
+          <t>KEPOLISIAN NEGARA REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6870,39 +6868,39 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>034001002800301</t>
+          <t>019301003548301</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>RKK BNN OPS</t>
+          <t>RKK POLRI OPS</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>650901110791000</t>
+          <t>652376653071000</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>BPG 109 BNNK OKUT MARTAPURA</t>
+          <t>BPG 109 POLRES OKU SELATAN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>10385944</t>
+          <t>220000000</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="Q49" t="n">
-        <v>235865601</v>
+        <v>310210000</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -6911,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4332775639</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -6946,19 +6944,19 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665307</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6968,12 +6966,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN NARKOTIKA NASIONAL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6983,12 +6981,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN NARKOTIKA NASIONAL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7003,45 +7001,45 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>050601000144309</t>
+          <t>034001002800301</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMU</t>
+          <t>RKK BNN OPS</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>651896565531000</t>
+          <t>650901110791000</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKU</t>
+          <t>BPG 109 BNNK OKUT MARTAPURA</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>10385944</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="Q50" t="n">
-        <v>69465184</v>
+        <v>235865601</v>
       </c>
       <c r="R50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1992710</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -7079,19 +7077,19 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>111079</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7121,7 +7119,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7136,7 +7134,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7151,30 +7149,30 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>651896565601000</t>
+          <t>651896565531000</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKUT</t>
+          <t>BPG 109 KPU OKU</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="Q51" t="n">
-        <v>95842429</v>
+        <v>69465184</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1992710</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -7212,19 +7210,19 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>656553</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7234,27 +7232,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN </t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7269,39 +7267,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>032901006291300</t>
+          <t>050601000144309</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
+          <t>KOMISI PEMILIHAN UMU</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>655026923341000</t>
+          <t>651896565601000</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>BPG 109 LP KLS IIB MUARADUA</t>
+          <t>BPG 109 KPU OKUT</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>95842429</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -7310,14 +7308,14 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>324000000</v>
+        <v>0</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7345,19 +7343,19 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7387,7 +7385,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7402,7 +7400,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7417,24 +7415,24 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>655026923391000</t>
+          <t>655026923341000</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>BPG 109 RUTAN KLS IIB BATURAJA</t>
+          <t>BPG 109 LP KLS IIB MUARADUA</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2199620</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>98966152</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7443,14 +7441,14 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>324000000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7478,19 +7476,19 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7520,7 +7518,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7535,7 +7533,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7550,24 +7548,24 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>655026923401000</t>
+          <t>655026923391000</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>BPG 109 LP KLS IIB MARTAPURA</t>
+          <t>BPG 109 RUTAN KLS IIB BATURAJA</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2992280</t>
+          <t>2199620</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="Q54" t="n">
-        <v>8235954</v>
+        <v>98966152</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7576,10 +7574,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>182353120</v>
+        <v>0</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7611,19 +7609,19 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692339</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7653,7 +7651,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7668,7 +7666,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7683,24 +7681,24 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>655026926251000</t>
+          <t>655026923401000</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>BPG 109 BAPAS KLS II OKU INDUK</t>
+          <t>BPG 109 LP KLS IIB MARTAPURA</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2992280</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="n">
-        <v>25092500</v>
+        <v>8235954</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -7709,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U55" t="n">
-        <v>33250000</v>
+        <v>182353120</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -7744,49 +7742,49 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692340</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BNI</t>
+          <t>BRI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BADAN PENGAWASAN PEMILIHAN UMUM</t>
+          <t xml:space="preserve">KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sekretariat Jenderal Badan Pengawas Pemilihan Umum</t>
+          <t>DIREKTORAT JENDERAL PEMASYARAKATAN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7801,39 +7799,39 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>969549335</t>
+          <t>032901006291300</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>RKK BAWASLU OPS                  PEMERINTAH</t>
+          <t>RKK DITJEN PEMASYARAKATAN KEM IMIPAS OPS</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>9890714190061000</t>
+          <t>655026926251000</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>BPG 109 SEKRET. BAWASLU KAB OKU</t>
+          <t>BPG 109 BAPAS KLS II OKU INDUK</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>1150000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="Q56" t="n">
-        <v>59877555</v>
+        <v>25092500</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -7842,10 +7840,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>4322500</v>
+        <v>33250000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -7877,19 +7875,19 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>692625</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7919,7 +7917,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7934,39 +7932,39 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2222227732</t>
+          <t>969549335</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>RKL SETJEN BAWASLU PDHL</t>
+          <t>RKK BAWASLU OPS                  PEMERINTAH</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>9897326865032401</t>
+          <t>9890714190061000</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>RPL109 PDHL PILBUP OKUS 2QPDXATA</t>
+          <t>BPG 109 SEKRET. BAWASLU KAB OKU</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1150000</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>59877555</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -7975,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>4322500</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -8010,19 +8008,19 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>419006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8032,12 +8030,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>BADAN PENGAWASAN PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8047,12 +8045,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>Sekretariat Jenderal Badan Pengawas Pemilihan Umum</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8067,39 +8065,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>976288077</t>
+          <t>2222227732</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>RKK KOMISI PEMILIHAN UMUM OPS           LAIN-LAIN</t>
+          <t>RKL SETJEN BAWASLU PDHL</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>9890766565741000</t>
+          <t>9897326865032401</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>BPG 109 KPU OKUS</t>
+          <t>RPL109 PDHL PILBUP OKUS 2QPDXATA</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>1785000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>60329827</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -8108,19 +8106,19 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>52206500</v>
+        <v>0</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -8143,19 +8141,19 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>686503</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8165,12 +8163,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8180,12 +8178,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>KOMISI PEMILIHAN UMUM</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8200,39 +8198,39 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2020090032</t>
+          <t>976288077</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>RKK KOMISI PEMILIHAN UMUM OPS           LAIN-LAIN</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>9890356705611000</t>
+          <t>9890766565741000</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KANTAH OKUS </t>
+          <t>BPG 109 KPU OKUS</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>6936601</t>
+          <t>1785000</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="Q59" t="n">
-        <v>144135223</v>
+        <v>60329827</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8241,10 +8239,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="U59" t="n">
-        <v>48074833</v>
+        <v>52206500</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8276,19 +8274,19 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8298,27 +8296,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8333,39 +8331,39 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>6072020860</t>
+          <t>2020090032</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS      PEMERINTAH</t>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>9891225537921000</t>
+          <t>9890356705611000</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>BPG 109 MTSN 1 OKU SELATAN</t>
+          <t xml:space="preserve">BPG 109 KANTAH OKUS </t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>13573000</t>
+          <t>6936601</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="Q60" t="n">
-        <v>58000</v>
+        <v>144135223</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -8374,10 +8372,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>429241000</v>
+        <v>48074833</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8409,19 +8407,19 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8451,7 +8449,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8466,7 +8464,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8481,24 +8479,24 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>9891226621271000</t>
+          <t>9891225537921000</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 MANMUARADUA </t>
+          <t>BPG 109 MTSN 1 OKU SELATAN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13573000</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -8507,14 +8505,14 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="U61" t="n">
-        <v>81278880</v>
+        <v>429241000</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8542,49 +8540,49 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bank Mandiri</t>
+          <t>BNI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KEMENTERIAN TRANSMIGRASI</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DIREKTORAT JENDERAL PEMBANGUNAN DAN PENGEMBANGAN KAWASAN TRANSMIGRASI</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8599,27 +8597,27 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Dinas Tenaga Kerja dan Transmgirasi Kabupaten Ogan Komering Ulu Timur</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1240018189994</t>
+          <t>6072020860</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>RKK DITJEN PPKTRANS</t>
+          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS      PEMERINTAH</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>8100126916531000</t>
+          <t>9891226621271000</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>BPG 109 DINAKERTRANS KAB OKU TIMUR</t>
+          <t xml:space="preserve">BPG 109 MANMUARADUA </t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -8640,10 +8638,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>81278880</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -8652,7 +8650,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -8675,19 +8673,19 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>662127</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8697,12 +8695,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>KEMENTERIAN TRANSMIGRASI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8712,12 +8710,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
+          <t>DIREKTORAT JENDERAL PEMBANGUNAN DAN PENGEMBANGAN KAWASAN TRANSMIGRASI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8732,39 +8730,39 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>Dinas Tenaga Kerja dan Transmgirasi Kabupaten Ogan Komering Ulu Timur</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1030093939342</t>
+          <t>1240018189994</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS ISLAM KEMENAG OPS</t>
+          <t>RKK DITJEN PPKTRANS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>8100124184571000</t>
+          <t>8100126916531000</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG03 OKU</t>
+          <t>BPG 109 DINAKERTRANS KAB OKU TIMUR</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>7500000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>178181713</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8780,12 +8778,12 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -8808,19 +8806,19 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>691653</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8840,17 +8838,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT ISLAM</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8870,34 +8868,34 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1030093939367</t>
+          <t>1030093939342</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS ISLAM KEMENAG OPS</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>8100124184601000</t>
+          <t>8100124184571000</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG07 OKU</t>
+          <t>BPG 109 MENAG03 OKU</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7500000</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>178181713</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -8913,12 +8911,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Inaktif CMS</t>
+          <t>Aktif CMS</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Tidak Aktif Transaksi</t>
+          <t>Aktif Transaksi</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -8941,19 +8939,19 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>418460</t>
+          <t>418457</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8973,17 +8971,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT HINDU</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9003,22 +9001,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1030009004009</t>
+          <t>1030093939367</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>RKK DITJEN PHU KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>8100124184611000</t>
+          <t>8100124184601000</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG 09 OKU</t>
+          <t>BPG 109 MENAG07 OKU</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -9074,19 +9072,19 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418460</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9106,17 +9104,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DITJEN PENDIDIKAN ISLAM</t>
+          <t>DITJEN PENYELENGGARAAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9131,39 +9129,39 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KOTA PALEMBANG</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1030093939391</t>
+          <t>1030009004009</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS</t>
+          <t>RKK DITJEN PHU KEMENAG OPS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>8100124184581000</t>
+          <t>8100124184611000</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>BPG109 MENAG 04 OKU</t>
+          <t>BPG 109 MENAG 09 OKU</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>3655100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>160287701</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -9179,12 +9177,12 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Aktif CMS</t>
+          <t>Inaktif CMS</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Aktif Transaksi</t>
+          <t>Tidak Aktif Transaksi</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -9207,19 +9205,19 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418461</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9229,12 +9227,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -9244,12 +9242,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>DITJEN PENDIDIKAN ISLAM</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -9264,39 +9262,39 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KOTA PALEMBANG</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1190066371202</t>
+          <t>1030093939391</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG OPS</t>
+          <t>RKK DITJEN PENDIDIKAN ISLAM KEMENAG OPS</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>8100124022681000</t>
+          <t>8100124184581000</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>BPG 109 PA_BATURAJA_BPU</t>
+          <t>BPG109 MENAG 04 OKU</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3655100</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="Q67" t="n">
-        <v>23880000</v>
+        <v>160287701</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -9340,19 +9338,19 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>418458</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9362,34 +9360,34 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ditjen Badan Peradilan Agama</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>402268</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>418459</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>109</t>
@@ -9397,27 +9395,27 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1030055695569</t>
+          <t>1190066371202</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>RKK DITJEN BIMAS KATOLIK KEMENAG OPS</t>
+          <t>RKK DITJEN BADILAG OPS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>8100124184591000</t>
+          <t>8100124022681000</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG06 OKU</t>
+          <t>BPG 109 PA_BATURAJA_BPU</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -9426,10 +9424,10 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="Q68" t="n">
-        <v>20564000</v>
+        <v>23880000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -9473,19 +9471,19 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>402268</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9505,17 +9503,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL</t>
+          <t>DITJEN BIMBINGAN MASYARAKAT KATOLIK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9535,34 +9533,34 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1030093939334</t>
+          <t>1030055695569</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>RKK SEKRETARIAT JENDERAL KEMENAG OPS</t>
+          <t>RKK DITJEN BIMAS KATOLIK KEMENAG OPS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>8100124184561000</t>
+          <t>8100124184591000</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>BPG 109 MENAG 01 OKU</t>
+          <t>BPG 109 MENAG06 OKU</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>4825000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="Q69" t="n">
-        <v>153367917</v>
+        <v>20564000</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -9606,19 +9604,19 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9628,12 +9626,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -9648,7 +9646,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9663,39 +9661,39 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1260007919292</t>
+          <t>1030093939334</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>RKK SETJEN ATR OPS</t>
+          <t>RKK SEKRETARIAT JENDERAL KEMENAG OPS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>8100124311421000</t>
+          <t>8100124184561000</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">BPG 109 KANTAH OKU </t>
+          <t>BPG 109 MENAG 01 OKU</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>4825000</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="Q70" t="n">
-        <v>26856800</v>
+        <v>153367917</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -9704,10 +9702,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>381093872</v>
+        <v>0</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -9739,19 +9737,19 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418456</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9761,27 +9759,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>KEMENTERIAN AGRARIA DAN TATA RUANG/BPN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DITJEN PERBENDAHARAAN</t>
+          <t>SEKRETARIAT JENDERAL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9796,39 +9794,39 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1030020030009</t>
+          <t>1260007919292</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>RKK DITJEN PERBENDAHARAAN</t>
+          <t>RKK SETJEN ATR OPS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>8100125279751000</t>
+          <t>8100124311421000</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>BPG 109 KPPN BATURAJA</t>
+          <t xml:space="preserve">BPG 109 KANTAH OKU </t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>16141635</t>
+          <t>450</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="Q71" t="n">
-        <v>115384194</v>
+        <v>26856800</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -9837,10 +9835,10 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U71" t="n">
-        <v>177094803</v>
+        <v>381093872</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -9872,49 +9870,49 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>431142</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BSI</t>
+          <t>Bank Mandiri</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>DITJEN PERBENDAHARAAN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9929,39 +9927,39 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1999299918</t>
+          <t>1030020030009</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>RKK KEMENHAJ RI OPS</t>
+          <t>RKK DITJEN PERBENDAHARAAN</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>8101626951821000</t>
+          <t>8100125279751000</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU TIMUR</t>
+          <t>BPG 109 KPPN BATURAJA</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>5948000</t>
+          <t>16141635</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q72" t="n">
-        <v>215651538</v>
+        <v>115384194</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -9970,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>177094803</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -9987,7 +9985,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="Y72" t="n">
@@ -10005,19 +10003,19 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>527975</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10047,7 +10045,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10062,7 +10060,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10077,24 +10075,24 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>8101626951761000</t>
+          <t>8101626951821000</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU</t>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>5896000</t>
+          <t>5948000</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="Q73" t="n">
-        <v>361790608</v>
+        <v>215651538</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -10138,19 +10136,19 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10160,27 +10158,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MAHKAMAH AGUNG</t>
+          <t>KEMENTERIAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ditjen Badan Peradilan Agama</t>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10195,39 +10193,39 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>7811122275</t>
+          <t>1999299918</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>RKK DITJEN BADILAG OPS</t>
+          <t>RKK KEMENHAJ RI OPS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>8100124034091000</t>
+          <t>8101626951761000</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>BPG 109 PA MARTAPURA 04</t>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>1602000</t>
+          <t>5896000</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="Q74" t="n">
-        <v>49172000</v>
+        <v>361790608</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -10271,19 +10269,19 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>695176</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10293,27 +10291,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+          <t>Ditjen Badan Peradilan Agama</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10328,39 +10326,39 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1999299918</t>
+          <t>7811122275</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>RKK KEMENHAJ RI OPS</t>
+          <t>RKK DITJEN BADILAG OPS</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>8101626951841000</t>
+          <t>8100124034091000</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU SELATAN</t>
+          <t>BPG 109 PA MARTAPURA 04</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>6000000</t>
+          <t>1602000</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="Q75" t="n">
-        <v>99752552</v>
+        <v>49172000</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -10404,10 +10402,143 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
+          <t>403409</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>403409</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>27057</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BSI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN HAJI DAN UMRAH</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT JENDERAL KEMENTERIAN HAJI DAN UMRAH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>695184</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1999299918</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>RKK KEMENHAJ RI OPS</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>8101626951841000</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>BPG 109 KANTOR KEMENHAJ KAB OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>6000000</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>99752552</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Aktif CMS</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Aktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>TW2</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>695184</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
         <is>
           <t>695184</t>
         </is>
